--- a/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,7 +235,7 @@
     <t>166</t>
   </si>
   <si>
-    <t>Etablissement d'accueil mère-enfant</t>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
   </si>
   <si>
     <t>172</t>
@@ -382,24 +382,12 @@
     <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
   </si>
   <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire station nomades</t>
-  </si>
-  <si>
     <t>219</t>
   </si>
   <si>
     <t>Autre centre d'accueil</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre social</t>
-  </si>
-  <si>
     <t>221</t>
   </si>
   <si>
@@ -559,7 +547,7 @@
     <t>286</t>
   </si>
   <si>
-    <t>Club, Equipe de prévention</t>
+    <t>Service de prévention spécialisée</t>
   </si>
   <si>
     <t>292</t>
@@ -586,12 +574,6 @@
     <t>Ecole formant aux professions sanitaires</t>
   </si>
   <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Logement foyer non spécialisé</t>
-  </si>
-  <si>
     <t>330</t>
   </si>
   <si>
@@ -622,12 +604,6 @@
     <t>Service délégué aux prestations familiales</t>
   </si>
   <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Service de tutelle aux prestations sociales adultes</t>
-  </si>
-  <si>
     <t>347</t>
   </si>
   <si>
@@ -646,12 +622,6 @@
     <t>Centre hospitalier (CH)</t>
   </si>
   <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Centre circonscription sanitaire et sociale</t>
-  </si>
-  <si>
     <t>362</t>
   </si>
   <si>
@@ -736,30 +706,12 @@
     <t>Foyer d'hébergement pour enfants et adolescents handicapés</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Centre de services pour associations</t>
-  </si>
-  <si>
     <t>402</t>
   </si>
   <si>
     <t>Jardin d'enfants spécialisé</t>
   </si>
   <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Service social spécialisé ou polyvalent de catégorie</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Service social polyvalent de secteur</t>
-  </si>
-  <si>
     <t>411</t>
   </si>
   <si>
@@ -1142,6 +1094,12 @@
   </si>
   <si>
     <t>Centre de santé et de médiation en santé sexuelle</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
   </si>
   <si>
     <t>695</t>
@@ -1496,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B187"/>
+  <dimension ref="A1:B180"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2932,71 +2890,15 @@
         <v>382</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -3023,7 +2925,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -3031,42 +2933,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>401</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>405</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>406</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1160,6 +1160,12 @@
   </si>
   <si>
     <t>Autre service territorial</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
   </si>
   <si>
     <t/>
@@ -1454,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B180"/>
+  <dimension ref="A1:B181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2890,15 +2896,23 @@
         <v>382</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>384</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2939,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -2933,42 +2947,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -214,12 +214,6 @@
     <t>Centre médico-psychologique (CMP)</t>
   </si>
   <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
     <t>161</t>
   </si>
   <si>
@@ -427,7 +421,7 @@
     <t>236</t>
   </si>
   <si>
-    <t>Centre de placement familial socio-éducatif (CPFSE)</t>
+    <t>Service de placement familial (SPF)</t>
   </si>
   <si>
     <t>238</t>
@@ -1460,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B180"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2896,23 +2890,15 @@
         <v>382</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>384</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -2939,7 +2925,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>41</v>
@@ -2947,42 +2933,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
